--- a/Outputs/Scenarios/PtX_demand_PL_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_PL_Electrification.xlsx
@@ -495,7 +495,7 @@
         <v>2030</v>
       </c>
       <c r="C2" t="n">
-        <v>0.02206692631524506</v>
+        <v>0.02206692631524507</v>
       </c>
       <c r="D2" t="n">
         <v>0.0323190297383994</v>
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.003107897515646728</v>
+        <v>0.003107897515646727</v>
       </c>
     </row>
     <row r="32">
@@ -1999,7 +1999,7 @@
         <v>0.000804823610415823</v>
       </c>
       <c r="K42" t="n">
-        <v>0.003107897515646728</v>
+        <v>0.003107897515646727</v>
       </c>
     </row>
     <row r="43">

--- a/Outputs/Scenarios/PtX_demand_PL_Electrification.xlsx
+++ b/Outputs/Scenarios/PtX_demand_PL_Electrification.xlsx
@@ -1037,7 +1037,7 @@
         <v>0.01032955500440896</v>
       </c>
       <c r="K16" t="n">
-        <v>0.003167533039476586</v>
+        <v>0.003376484447995585</v>
       </c>
     </row>
     <row r="17">
@@ -1074,7 +1074,7 @@
         <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>0.0005279221732460977</v>
+        <v>0.0006989346058959548</v>
       </c>
     </row>
     <row r="18">
@@ -1111,7 +1111,7 @@
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>0.002111688692984391</v>
+        <v>0.002795738423583819</v>
       </c>
     </row>
     <row r="19">
@@ -1148,7 +1148,7 @@
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>0.003167533039476586</v>
+        <v>0.002795738423583819</v>
       </c>
     </row>
     <row r="20">
@@ -1333,7 +1333,7 @@
         <v>0.000827812464420179</v>
       </c>
       <c r="K24" t="n">
-        <v>0.004386594169003236</v>
+        <v>0.004306571495102604</v>
       </c>
     </row>
     <row r="25">
@@ -1370,7 +1370,7 @@
         <v>0.005010750588703055</v>
       </c>
       <c r="K25" t="n">
-        <v>0.04293306650751986</v>
+        <v>0.04214985779289511</v>
       </c>
     </row>
     <row r="26">
@@ -1481,7 +1481,7 @@
         <v>0.0001488314026094087</v>
       </c>
       <c r="K28" t="n">
-        <v>0.0005279221732460977</v>
+        <v>0.0006989346058959548</v>
       </c>
     </row>
     <row r="29">
@@ -1555,7 +1555,7 @@
         <v>0.01529164859790063</v>
       </c>
       <c r="K30" t="n">
-        <v>0.01864738509388036</v>
+        <v>0.01822215954322981</v>
       </c>
     </row>
     <row r="31">
@@ -1592,7 +1592,7 @@
         <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>0.003107897515646727</v>
+        <v>0.003771999573841128</v>
       </c>
     </row>
     <row r="32">
@@ -1629,7 +1629,7 @@
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>0.01243159006258691</v>
+        <v>0.01508799829536451</v>
       </c>
     </row>
     <row r="33">
@@ -1666,7 +1666,7 @@
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>0.01864738509388036</v>
+        <v>0.01508799829536451</v>
       </c>
     </row>
     <row r="34">
@@ -1999,7 +1999,7 @@
         <v>0.000804823610415823</v>
       </c>
       <c r="K42" t="n">
-        <v>0.003107897515646727</v>
+        <v>0.003771999573841128</v>
       </c>
     </row>
     <row r="43">
